--- a/static/data/exports/Retro_TR_AE_2018.xlsx
+++ b/static/data/exports/Retro_TR_AE_2018.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_TR_AE_2018.xlsx
+++ b/static/data/exports/Retro_TR_AE_2018.xlsx
@@ -602,11 +602,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E3" t="n">
         <v>14014</v>
@@ -1036,11 +1036,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E10" t="n">
         <v>17340</v>
@@ -1346,11 +1346,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E15" t="n">
         <v>19042</v>
@@ -1718,11 +1718,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E21" t="n">
         <v>15825</v>
@@ -2090,11 +2090,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E27" t="n">
         <v>18457</v>
@@ -2400,11 +2400,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E32" t="n">
         <v>17852</v>
@@ -2772,11 +2772,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E38" t="n">
         <v>16237</v>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E48" t="n">
         <v>12206</v>
@@ -3950,11 +3950,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E57" t="n">
         <v>19359</v>
@@ -4198,11 +4198,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E61" t="n">
         <v>15517</v>
@@ -4570,11 +4570,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E67" t="n">
         <v>9404</v>
@@ -4942,11 +4942,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E73" t="n">
         <v>22686</v>
@@ -5314,11 +5314,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E79" t="n">
         <v>23113</v>
@@ -5624,11 +5624,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E84" t="n">
         <v>18847</v>
@@ -5996,11 +5996,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E90" t="n">
         <v>21254</v>
@@ -6368,11 +6368,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E96" t="n">
         <v>15730</v>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E101" t="n">
         <v>20307</v>
@@ -7112,11 +7112,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E108" t="n">
         <v>1030</v>
@@ -7422,11 +7422,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E113" t="n">
         <v>19862</v>
@@ -7794,11 +7794,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E119" t="n">
         <v>18810</v>
@@ -8042,11 +8042,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E123" t="n">
         <v>19275</v>
@@ -8414,11 +8414,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E129" t="n">
         <v>22176</v>
@@ -8786,11 +8786,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E135" t="n">
         <v>15204</v>
@@ -9034,11 +9034,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E139" t="n">
         <v>20629</v>
@@ -9406,11 +9406,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E145" t="n">
         <v>12201</v>
@@ -9840,11 +9840,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E152" t="n">
         <v>17152</v>
@@ -10212,11 +10212,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E158" t="n">
         <v>14898</v>
@@ -10584,11 +10584,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E164" t="n">
         <v>14735</v>
@@ -10894,11 +10894,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E169" t="n">
         <v>21241</v>
@@ -11576,11 +11576,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E180" t="n">
         <v>21500</v>
@@ -12010,11 +12010,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E187" t="n">
         <v>24835</v>
@@ -12196,11 +12196,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E190" t="n">
         <v>22004</v>
@@ -12630,11 +12630,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E197" t="n">
         <v>18554</v>
@@ -13312,11 +13312,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E208" t="n">
         <v>22673</v>
@@ -13622,11 +13622,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E213" t="n">
         <v>21160</v>
@@ -13994,11 +13994,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E219" t="n">
         <v>19432</v>
@@ -14366,11 +14366,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E225" t="n">
         <v>18877</v>
@@ -14676,11 +14676,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E230" t="n">
         <v>13255</v>
@@ -14986,11 +14986,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E235" t="n">
         <v>17954</v>
@@ -15420,11 +15420,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E242" t="n">
         <v>14825</v>
@@ -15854,11 +15854,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E249" t="n">
         <v>16751</v>
@@ -16288,11 +16288,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E256" t="n">
         <v>17206</v>
@@ -16660,11 +16660,11 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E262" t="n">
         <v>18057</v>
@@ -17094,11 +17094,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E269" t="n">
         <v>17257</v>
@@ -17466,11 +17466,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E275" t="n">
         <v>12061</v>
@@ -17900,11 +17900,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E282" t="n">
         <v>14535</v>
@@ -18334,11 +18334,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E289" t="n">
         <v>16988</v>
@@ -18706,11 +18706,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E295" t="n">
         <v>16683</v>
@@ -19016,11 +19016,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E300" t="n">
         <v>18545</v>
@@ -19317,20 +19317,20 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>1782549</v>
+        <v>1782550</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Bidyut Bikash Singha</t>
+          <t>Gouranga Debnath</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>AITC</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>22928</v>
+        <v>22936</v>
       </c>
       <c r="E305" t="n">
         <v>189</v>
@@ -19354,12 +19354,12 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Bidyut Bikash Singha</t>
+          <t>Gouranga Debnath</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>AITC</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="Q305" t="b">
@@ -19379,20 +19379,20 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>1782550</v>
+        <v>1782549</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Gouranga Debnath</t>
+          <t>Bidyut Bikash Singha</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>AITC</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>22936</v>
+        <v>22928</v>
       </c>
       <c r="E306" t="n">
         <v>189</v>
@@ -19416,12 +19416,12 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Gouranga Debnath</t>
+          <t>Bidyut Bikash Singha</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>AITC</t>
         </is>
       </c>
       <c r="Q306" t="b">
@@ -19450,11 +19450,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E307" t="n">
         <v>18093</v>
@@ -19760,11 +19760,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E312" t="n">
         <v>20721</v>
@@ -20194,11 +20194,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E319" t="n">
         <v>18001</v>
@@ -20690,11 +20690,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E327" t="n">
         <v>14070</v>
@@ -21062,11 +21062,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E333" t="n">
         <v>18147</v>
@@ -21496,11 +21496,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E340" t="n">
         <v>15331</v>
@@ -21868,11 +21868,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E346" t="n">
         <v>16370</v>
@@ -22302,11 +22302,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E353" t="n">
         <v>15317</v>
